--- a/SGC-CKN/Excel/9c1a1dd8-cd7e-4c45-b62f-7c826889942a_Lô_CT-02_P8-9_D800_06-04-2026.xlsx
+++ b/SGC-CKN/Excel/9c1a1dd8-cd7e-4c45-b62f-7c826889942a_Lô_CT-02_P8-9_D800_06-04-2026.xlsx
@@ -53,7 +53,7 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>15:00 05/04/2026</t>
+    <t>18:00 05/04/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
@@ -95,10 +95,10 @@
     <t>1</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:00
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:00
 05/04/2026</t>
   </si>
   <si>
@@ -112,14 +112,14 @@
     <t>2</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha, xám ghi, xám nâu, xám vàng, TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">18:18
 05/04/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">18:42
+    <t xml:space="preserve">18:23
 05/04/2026</t>
   </si>
   <si>
@@ -130,6 +130,10 @@
   </si>
   <si>
     <t>Sét xám trắng, xám xanh dẻo chảy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19:30
+05/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">20:25
@@ -142,7 +146,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">20:26
@@ -159,7 +163,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">21:01
@@ -176,7 +180,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
+    <t>Cát thô, xám vàng, xám xanh, xám nâu, KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">21:41
@@ -193,7 +197,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">22:31
@@ -210,7 +214,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>Cát xám, xám vàng, xám xanh, TT rất chặt</t>
+    <t>Cát xạm, xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">01:00
@@ -227,9 +231,6 @@
     <t>9</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
-  </si>
-  <si>
     <t xml:space="preserve">01:36
 06/04/2026</t>
   </si>
@@ -244,7 +245,7 @@
     <t>10</t>
   </si>
   <si>
-    <t>Cuội đa màu sắc TT rất chặt</t>
+    <t>Cuội đa màu sắc, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">03:31
@@ -417,17 +418,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFDE68A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -453,6 +449,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFED7AA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -598,53 +599,53 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1265,19 +1266,19 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-3.55</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-7.22</v>
       </c>
       <c r="H11" s="5">
-        <v>3.28</v>
+        <v>0.28</v>
       </c>
       <c r="I11" s="5">
-        <v>3.67</v>
+        <v>7.22</v>
       </c>
       <c r="J11" s="8">
-        <v>1.12</v>
+        <v>25.48</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1306,208 +1307,208 @@
         <v>-9.22</v>
       </c>
       <c r="H12" s="9">
-        <v>0.4</v>
+        <v>0.08</v>
       </c>
       <c r="I12" s="9">
         <v>2</v>
       </c>
-      <c r="J12" s="12">
-        <v>5</v>
+      <c r="J12" s="8">
+        <v>24</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" s="15" t="s">
+      <c r="D13" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="13">
+      <c r="E13" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="12">
         <v>-9.22</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="12">
         <v>-17.42</v>
       </c>
-      <c r="H13" s="13">
-        <v>1.72</v>
-      </c>
-      <c r="I13" s="13">
+      <c r="H13" s="12">
+        <v>0.92</v>
+      </c>
+      <c r="I13" s="12">
         <v>8.2</v>
       </c>
       <c r="J13" s="8">
-        <v>4.78</v>
-      </c>
-      <c r="K13" s="14" t="s">
-        <v>39</v>
+        <v>8.95</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="16" t="s">
+      <c r="A14" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="18" t="s">
+      <c r="C14" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="D14" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="16">
+      <c r="E14" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="15">
         <v>-17.42</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="15">
         <v>-21.7</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="15">
         <v>0.57</v>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="15">
         <v>4.28</v>
       </c>
-      <c r="J14" s="12">
+      <c r="J14" s="8">
         <v>7.55</v>
       </c>
-      <c r="K14" s="17" t="s">
-        <v>44</v>
+      <c r="K14" s="16" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B15" s="19" t="s">
+      <c r="A15" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" s="21" t="s">
+      <c r="C15" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="D15" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F15" s="19">
+      <c r="E15" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" s="18">
         <v>-21.7</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="18">
         <v>-26.5</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="18">
         <v>0.65</v>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="18">
         <v>4.8</v>
       </c>
-      <c r="J15" s="12">
+      <c r="J15" s="8">
         <v>7.38</v>
       </c>
-      <c r="K15" s="20" t="s">
-        <v>49</v>
+      <c r="K15" s="19" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="B16" s="22" t="s">
+      <c r="A16" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" s="24" t="s">
+      <c r="C16" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="D16" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="22">
+      <c r="E16" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" s="21">
         <v>-26.5</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="21">
         <v>-36.21</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="21">
         <v>0.82</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16" s="21">
         <v>9.71</v>
       </c>
-      <c r="J16" s="12">
+      <c r="J16" s="8">
         <v>11.89</v>
       </c>
-      <c r="K16" s="23" t="s">
-        <v>54</v>
+      <c r="K16" s="22" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="B17" s="25" t="s">
+      <c r="A17" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" s="27" t="s">
+      <c r="C17" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="D17" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="F17" s="25">
+      <c r="E17" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="F17" s="24">
         <v>-36.21</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="24">
         <v>-38.45</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="24">
         <v>0.48</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="24">
         <v>2.24</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J17" s="27">
         <v>4.63</v>
       </c>
-      <c r="K17" s="26" t="s">
-        <v>59</v>
+      <c r="K17" s="25" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F18" s="28">
         <v>-38.45</v>
@@ -1521,22 +1522,22 @@
       <c r="I18" s="28">
         <v>1.55</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="27">
         <v>2.66</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D19" s="33" t="s">
         <v>67</v>
@@ -1556,7 +1557,7 @@
       <c r="I19" s="31">
         <v>3.25</v>
       </c>
-      <c r="J19" s="8">
+      <c r="J19" s="27">
         <v>1.71</v>
       </c>
       <c r="K19" s="32" t="s">
@@ -1591,7 +1592,7 @@
       <c r="I20" s="34">
         <v>1.55</v>
       </c>
-      <c r="J20" s="8">
+      <c r="J20" s="27">
         <v>1.75</v>
       </c>
       <c r="K20" s="35" t="s">
@@ -1747,19 +1748,19 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-3.55</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-7.22</v>
       </c>
       <c r="G2" s="5">
-        <v>3.28</v>
+        <v>0.28</v>
       </c>
       <c r="H2" s="5">
-        <v>3.67</v>
+        <v>7.22</v>
       </c>
       <c r="I2" s="8">
-        <v>1.12</v>
+        <v>25.48</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1782,157 +1783,157 @@
         <v>-9.22</v>
       </c>
       <c r="G3" s="9">
-        <v>0.4</v>
+        <v>0.08</v>
       </c>
       <c r="H3" s="9">
         <v>2</v>
       </c>
-      <c r="I3" s="12">
+      <c r="I3" s="8">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="12">
+        <v>3</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="12">
+        <v>1</v>
+      </c>
+      <c r="E4" s="12">
+        <v>-9.22</v>
+      </c>
+      <c r="F4" s="12">
+        <v>-17.42</v>
+      </c>
+      <c r="G4" s="12">
+        <v>0.92</v>
+      </c>
+      <c r="H4" s="12">
+        <v>8.2</v>
+      </c>
+      <c r="I4" s="8">
+        <v>8.95</v>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="15">
+        <v>4</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="15">
+        <v>1</v>
+      </c>
+      <c r="E5" s="15">
+        <v>-17.42</v>
+      </c>
+      <c r="F5" s="15">
+        <v>-21.7</v>
+      </c>
+      <c r="G5" s="15">
+        <v>0.57</v>
+      </c>
+      <c r="H5" s="15">
+        <v>4.28</v>
+      </c>
+      <c r="I5" s="8">
+        <v>7.55</v>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="18">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
-        <v>3</v>
-      </c>
-      <c r="B4" s="13" t="s">
+      <c r="B6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="13">
+      <c r="C6" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="18">
         <v>1</v>
       </c>
-      <c r="E4" s="13">
-        <v>-9.22</v>
-      </c>
-      <c r="F4" s="13">
-        <v>-17.42</v>
-      </c>
-      <c r="G4" s="13">
-        <v>1.72</v>
-      </c>
-      <c r="H4" s="13">
-        <v>8.2</v>
-      </c>
-      <c r="I4" s="8">
-        <v>4.78</v>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
-        <v>4</v>
-      </c>
-      <c r="B5" s="16" t="s">
+      <c r="E6" s="18">
+        <v>-21.7</v>
+      </c>
+      <c r="F6" s="18">
+        <v>-26.5</v>
+      </c>
+      <c r="G6" s="18">
+        <v>0.65</v>
+      </c>
+      <c r="H6" s="18">
+        <v>4.8</v>
+      </c>
+      <c r="I6" s="8">
+        <v>7.38</v>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="21">
+        <v>6</v>
+      </c>
+      <c r="B7" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" s="16">
+      <c r="C7" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="21">
         <v>1</v>
       </c>
-      <c r="E5" s="16">
-        <v>-17.42</v>
-      </c>
-      <c r="F5" s="16">
-        <v>-21.7</v>
-      </c>
-      <c r="G5" s="16">
-        <v>0.57</v>
-      </c>
-      <c r="H5" s="16">
-        <v>4.28</v>
-      </c>
-      <c r="I5" s="12">
-        <v>7.55</v>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
-        <v>5</v>
-      </c>
-      <c r="B6" s="19" t="s">
+      <c r="E7" s="21">
+        <v>-26.5</v>
+      </c>
+      <c r="F7" s="21">
+        <v>-36.21</v>
+      </c>
+      <c r="G7" s="21">
+        <v>0.82</v>
+      </c>
+      <c r="H7" s="21">
+        <v>9.71</v>
+      </c>
+      <c r="I7" s="8">
+        <v>11.89</v>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="24">
+        <v>7</v>
+      </c>
+      <c r="B8" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="19">
+      <c r="C8" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="24">
         <v>1</v>
       </c>
-      <c r="E6" s="19">
-        <v>-21.7</v>
-      </c>
-      <c r="F6" s="19">
-        <v>-26.5</v>
-      </c>
-      <c r="G6" s="19">
-        <v>0.65</v>
-      </c>
-      <c r="H6" s="19">
-        <v>4.8</v>
-      </c>
-      <c r="I6" s="12">
-        <v>7.38</v>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="22">
-        <v>6</v>
-      </c>
-      <c r="B7" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="22">
-        <v>1</v>
-      </c>
-      <c r="E7" s="22">
-        <v>-26.5</v>
-      </c>
-      <c r="F7" s="22">
+      <c r="E8" s="24">
         <v>-36.21</v>
       </c>
-      <c r="G7" s="22">
-        <v>0.82</v>
-      </c>
-      <c r="H7" s="22">
-        <v>9.71</v>
-      </c>
-      <c r="I7" s="12">
-        <v>11.89</v>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="25">
-        <v>7</v>
-      </c>
-      <c r="B8" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" s="25">
-        <v>1</v>
-      </c>
-      <c r="E8" s="25">
-        <v>-36.21</v>
-      </c>
-      <c r="F8" s="25">
+      <c r="F8" s="24">
         <v>-38.45</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="24">
         <v>0.48</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="24">
         <v>2.24</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="27">
         <v>4.63</v>
       </c>
     </row>
@@ -1944,7 +1945,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1961,7 +1962,7 @@
       <c r="H9" s="28">
         <v>1.55</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="27">
         <v>2.66</v>
       </c>
     </row>
@@ -1973,7 +1974,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
@@ -1990,7 +1991,7 @@
       <c r="H10" s="31">
         <v>3.25</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="27">
         <v>1.71</v>
       </c>
     </row>
@@ -2019,7 +2020,7 @@
       <c r="H11" s="34">
         <v>1.55</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="27">
         <v>1.75</v>
       </c>
     </row>
@@ -2037,19 +2038,19 @@
         <v>10</v>
       </c>
       <c r="E12" s="39">
-        <v>-3.55</v>
+        <v>0</v>
       </c>
       <c r="F12" s="39">
         <v>-44.8</v>
       </c>
       <c r="G12" s="39">
-        <v>11.28</v>
+        <v>7.17</v>
       </c>
       <c r="H12" s="39">
-        <v>41.25</v>
+        <v>44.8</v>
       </c>
       <c r="I12" s="39">
-        <v>3.66</v>
+        <v>6.25</v>
       </c>
     </row>
   </sheetData>
